--- a/analisisdesuelo/Analisis_Compactacion/Analisis de compactación.xlsx
+++ b/analisisdesuelo/Analisis_Compactacion/Analisis de compactación.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/R MAC/ProyectosFlutter/agro_app/analisisdesuelo/Análisis Compactación/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/R MAC/ProyectosFlutter/src/flutter_projects/agro_app/analisisdesuelo/Analisis_Compactacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246E662F-2F84-CE4E-AD19-4C47E19751FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B57BFB-C2E8-084E-BAB4-FC5621E31E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{4C8774B1-5EC8-A140-93CD-E6428AFBC07A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4C8774B1-5EC8-A140-93CD-E6428AFBC07A}"/>
   </bookViews>
   <sheets>
     <sheet name="Recomendaciones" sheetId="2" r:id="rId1"/>
@@ -277,7 +277,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -811,6 +811,60 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -883,59 +937,53 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -943,24 +991,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -972,42 +1008,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4645,195 +4645,203 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29C44BAB-71C0-5D4C-BF4F-BB415B0326D6}">
   <dimension ref="A25:H42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="7" width="10.1640625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="25" spans="1:8" ht="17" thickBot="1">
-      <c r="A25" s="38" t="s">
+    <row r="25" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="39" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
     </row>
-    <row r="26" spans="1:8" ht="32" customHeight="1">
-      <c r="A26" s="48" t="s">
+    <row r="26" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48" t="s">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="48"/>
-      <c r="F26" s="42" t="s">
+      <c r="D26" s="24"/>
+      <c r="F26" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="43"/>
+      <c r="G26" s="19"/>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="49" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="50">
+      <c r="B27" s="25"/>
+      <c r="C27" s="26">
         <f>SUM('Diagnostico y acodicionamiento '!C20:C24)/5</f>
         <v>16.2</v>
       </c>
-      <c r="D27" s="51"/>
-      <c r="F27" s="44" t="s">
+      <c r="D27" s="27"/>
+      <c r="F27" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G27" s="45"/>
+      <c r="G27" s="21"/>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="49" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="52">
+      <c r="B28" s="25"/>
+      <c r="C28" s="28">
         <f>SUM('Diagnostico y acodicionamiento '!C25:C30)/6</f>
         <v>115.83333333333333</v>
       </c>
-      <c r="D28" s="53"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="45"/>
+      <c r="D28" s="29"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="49" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="54">
+      <c r="B29" s="25"/>
+      <c r="C29" s="30">
         <f>SUM('Diagnostico y acodicionamiento '!C31:C34)/4</f>
         <v>148.75</v>
       </c>
-      <c r="D29" s="55"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="45"/>
+      <c r="D29" s="31"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21"/>
     </row>
-    <row r="30" spans="1:8" ht="17" thickBot="1">
-      <c r="A30" s="40" t="s">
+    <row r="30" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="40">
+      <c r="B30" s="17"/>
+      <c r="C30" s="16">
         <f>'Diagnostico y acodicionamiento '!C35</f>
         <v>91.4</v>
       </c>
-      <c r="D30" s="41"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="47"/>
+      <c r="D30" s="17"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="23"/>
     </row>
-    <row r="31" spans="1:8" ht="17" thickBot="1"/>
-    <row r="32" spans="1:8" ht="31" customHeight="1">
-      <c r="A32" s="31" t="str">
+    <row r="31" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="49" t="str">
         <f>INDEX('Diagnostico y acodicionamiento '!A37:E42,MATCH(F27,'Diagnostico y acodicionamiento '!A37:A42,0),5)</f>
         <v>No requiere de Subsuelo</v>
       </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="29" t="str">
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="47" t="str">
         <f>INDEX('Diagnostico y acodicionamiento '!D20:G27,MATCH(F27,'Diagnostico y acodicionamiento '!D20:D27,0),2)</f>
         <v>Suelo en condiciones limitadas para establacer LC.</v>
       </c>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
     </row>
-    <row r="33" spans="1:8" ht="31" customHeight="1" thickBot="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="30" t="str">
+    <row r="33" spans="1:8" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="48" t="str">
         <f>INDEX('Diagnostico y acodicionamiento '!A37:D42,MATCH(F27,'Diagnostico y acodicionamiento '!A37:A42,0),2)</f>
         <v>Se Puede establecer LC. Bajo criterio de las otras variables</v>
       </c>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
     </row>
-    <row r="35" spans="1:8" ht="20" thickBot="1">
-      <c r="A35" s="37" t="s">
+    <row r="35" spans="1:8" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
     </row>
-    <row r="36" spans="1:8">
-      <c r="D36" s="14" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D36" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="27" t="s">
+      <c r="E36" s="33"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="28"/>
+      <c r="H36" s="46"/>
     </row>
-    <row r="37" spans="1:8">
-      <c r="D37" s="17" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D37" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="23" t="s">
+      <c r="E37" s="36"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="H37" s="24"/>
+      <c r="H37" s="42"/>
     </row>
-    <row r="38" spans="1:8">
-      <c r="D38" s="17"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="24"/>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D38" s="35"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="42"/>
     </row>
-    <row r="39" spans="1:8">
-      <c r="D39" s="17"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="24"/>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D39" s="35"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="42"/>
     </row>
-    <row r="40" spans="1:8">
-      <c r="D40" s="17"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="24"/>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D40" s="35"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="42"/>
     </row>
-    <row r="41" spans="1:8">
-      <c r="D41" s="17"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="24"/>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D41" s="35"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="42"/>
     </row>
-    <row r="42" spans="1:8" ht="17" thickBot="1">
-      <c r="D42" s="20"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="26"/>
+    <row r="42" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="38"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F42"/>
+    <mergeCell ref="G37:H42"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="A32:D33"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="E25:H25"/>
     <mergeCell ref="A30:B30"/>
@@ -4848,14 +4856,6 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F42"/>
-    <mergeCell ref="G37:H42"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="A32:D33"/>
-    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="A32:D33">
     <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="REQUIERE Subsuelo">
@@ -4895,7 +4895,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE2C1C9-6A09-4242-9D85-C28C52D5E3CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4905,7 +4905,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B61D16-BD8F-6D4E-A641-CB55BEBB17D9}">
   <dimension ref="A1:H42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.1640625" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
@@ -4914,20 +4914,20 @@
     <col min="8" max="8" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.2">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="17" thickBot="1"/>
-    <row r="19" spans="1:7" ht="35" thickBot="1">
+    <row r="18" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:7" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>3</v>
       </c>
@@ -4937,14 +4937,14 @@
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="79"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="71"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>1</v>
       </c>
@@ -4954,16 +4954,16 @@
       <c r="C20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E20" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="61"/>
-      <c r="G20" s="75"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
     </row>
-    <row r="21" spans="1:7" ht="17" thickBot="1">
+    <row r="21" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>2</v>
       </c>
@@ -4973,12 +4973,12 @@
       <c r="C21" s="4">
         <v>0</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="76"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="68"/>
     </row>
-    <row r="22" spans="1:7" ht="17" thickBot="1">
+    <row r="22" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>3</v>
       </c>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D22" s="5"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>4</v>
       </c>
@@ -5000,16 +5000,16 @@
       <c r="C23" s="4">
         <v>20</v>
       </c>
-      <c r="D23" s="58" t="s">
+      <c r="D23" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="61" t="s">
+      <c r="E23" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="61"/>
-      <c r="G23" s="75"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="66"/>
     </row>
-    <row r="24" spans="1:7" ht="17" thickBot="1">
+    <row r="24" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>5</v>
       </c>
@@ -5019,12 +5019,12 @@
       <c r="C24" s="4">
         <v>45</v>
       </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="76"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="68"/>
     </row>
-    <row r="25" spans="1:7" ht="17" thickBot="1">
+    <row r="25" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>6</v>
       </c>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>7</v>
       </c>
@@ -5046,16 +5046,16 @@
       <c r="C26" s="4">
         <v>130</v>
       </c>
-      <c r="D26" s="58" t="s">
+      <c r="D26" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="68"/>
-      <c r="G26" s="69"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="59"/>
     </row>
-    <row r="27" spans="1:7" ht="17" thickBot="1">
+    <row r="27" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>8</v>
       </c>
@@ -5065,12 +5065,12 @@
       <c r="C27" s="4">
         <v>140</v>
       </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="71"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="61"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>9</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>10</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>11</v>
       </c>
@@ -5102,14 +5102,14 @@
       <c r="C30" s="4">
         <v>115</v>
       </c>
-      <c r="D30" s="72" t="s">
+      <c r="D30" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
     </row>
-    <row r="31" spans="1:7" ht="16" customHeight="1">
+    <row r="31" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>12</v>
       </c>
@@ -5119,14 +5119,14 @@
       <c r="C31" s="4">
         <v>135</v>
       </c>
-      <c r="D31" s="73" t="s">
+      <c r="D31" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>13</v>
       </c>
@@ -5136,12 +5136,12 @@
       <c r="C32" s="4">
         <v>145</v>
       </c>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>14</v>
       </c>
@@ -5151,12 +5151,12 @@
       <c r="C33" s="4">
         <v>150</v>
       </c>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
     </row>
-    <row r="34" spans="1:7" ht="17" thickBot="1">
+    <row r="34" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>15</v>
       </c>
@@ -5166,12 +5166,12 @@
       <c r="C34" s="10">
         <v>165</v>
       </c>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="73"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
     </row>
-    <row r="35" spans="1:7" ht="17" thickBot="1">
+    <row r="35" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>4</v>
       </c>
@@ -5183,76 +5183,85 @@
         <f>(C20+C21+C22+C23+C24+C25+C26+C27+C28+C29+C30+C31+C32+C33+C34)/15</f>
         <v>91.4</v>
       </c>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
     </row>
-    <row r="36" spans="1:7" ht="17" thickBot="1"/>
-    <row r="37" spans="1:7">
-      <c r="A37" s="58" t="s">
+    <row r="36" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="56" t="s">
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="72" t="s">
         <v>27</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="17" thickBot="1">
-      <c r="A38" s="59"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="57"/>
+    <row r="38" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="57"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="73"/>
     </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="58" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="56" t="s">
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="72" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="17" thickBot="1">
-      <c r="A40" s="59"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="57"/>
+    <row r="40" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="57"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="73"/>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="58" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="65"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="56" t="s">
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="72" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="17" thickBot="1">
-      <c r="A42" s="59"/>
-      <c r="B42" s="66"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="57"/>
+    <row r="42" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="57"/>
+      <c r="B42" s="78"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:D38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:D40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:D42"/>
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="E26:G27"/>
     <mergeCell ref="D30:G30"/>
@@ -5263,15 +5272,6 @@
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="E23:G24"/>
     <mergeCell ref="D19:G19"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:D38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:D40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:D42"/>
   </mergeCells>
   <conditionalFormatting sqref="C20:C34">
     <cfRule type="cellIs" dxfId="5" priority="4" stopIfTrue="1" operator="between">
